--- a/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
+++ b/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
@@ -1,33 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ChrisitanRaun-AnnanasMotor\Design-Files\ControlBoard-DesignFiles\Project Outputs for Control_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F73E86-7770-4D62-BA0C-1900C44A77A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="14430"/>
+    <workbookView xWindow="7035" yWindow="300" windowWidth="10335" windowHeight="10620" xr2:uid="{CF46F1DC-E390-44DE-9ADC-5B141A9D882E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Control_Board" sheetId="1" r:id="rId1"/>
+    <sheet name="Altium Generated BOM Control_Bo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Control_Board!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Altium Generated BOM Control_Bo'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="124">
   <si>
     <t>Comment</t>
   </si>
@@ -155,13 +163,16 @@
     <t>PH254P1x12SMRA-100_1</t>
   </si>
   <si>
-    <t>PHF254SMD-x</t>
-  </si>
-  <si>
-    <t>P=2.54mm Female Headers,SMD,ROHS</t>
+    <t>95278-101A26LF</t>
+  </si>
+  <si>
+    <t>CONN HEADER SMD 26POS 2.54MM</t>
   </si>
   <si>
     <t>J3</t>
+  </si>
+  <si>
+    <t>Amphenol ICC (FCI)</t>
   </si>
   <si>
     <t>MLB1608-201P1A(f)</t>
@@ -401,7 +412,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -498,7 +509,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -510,7 +521,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -557,6 +568,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -592,6 +620,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -743,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D6868A-9F0A-4516-8463-638A210F92F4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -958,93 +1003,93 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F11" s="4">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="F12" s="4">
         <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="4">
         <v>3</v>
@@ -1053,19 +1098,19 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="4">
         <v>12</v>
@@ -1076,19 +1121,19 @@
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
@@ -1099,19 +1144,19 @@
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -1122,19 +1167,19 @@
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" s="4">
         <v>4</v>
@@ -1145,19 +1190,19 @@
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
@@ -1168,19 +1213,19 @@
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1191,19 +1236,19 @@
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
@@ -1214,19 +1259,19 @@
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" s="4">
         <v>5</v>
@@ -1235,163 +1280,163 @@
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="4">
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="4">
         <v>1</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="4">
         <v>1</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="4">
         <v>1</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F27" s="4">
         <v>1</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="4">
         <v>1</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
+++ b/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25219"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Control_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F73E86-7770-4D62-BA0C-1900C44A77A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AC89C4-0055-41EF-869B-C52B3F52D809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="300" windowWidth="10335" windowHeight="10620" xr2:uid="{CF46F1DC-E390-44DE-9ADC-5B141A9D882E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{CF46F1DC-E390-44DE-9ADC-5B141A9D882E}"/>
   </bookViews>
   <sheets>
     <sheet name="Altium Generated BOM Control_Bo" sheetId="1" r:id="rId1"/>
@@ -793,13 +793,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -822,7 +822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -845,7 +845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -868,7 +868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -914,7 +914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
@@ -937,7 +937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
@@ -960,7 +960,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
@@ -983,7 +983,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>64</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>73</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>85</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>89</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>96</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>100</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>108</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>112</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>116</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>120</v>
       </c>

--- a/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
+++ b/Deliverables/Control_Board/BOM/Altium Generated BOM Control_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AC89C4-0055-41EF-869B-C52B3F52D809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8637D911-D022-4768-A483-2FAA5B83CA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{CF46F1DC-E390-44DE-9ADC-5B141A9D882E}"/>
+    <workbookView xWindow="-5715" yWindow="3075" windowWidth="11790" windowHeight="15360" xr2:uid="{1FFED774-B8A0-4F3B-A8EF-6E3139B4D556}"/>
   </bookViews>
   <sheets>
     <sheet name="Altium Generated BOM Control_Bo" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="127">
   <si>
     <t>Comment</t>
   </si>
@@ -49,15 +50,15 @@
     <t>Footprint</t>
   </si>
   <si>
-    <t>LibRef</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
     <t>Manufacturer</t>
   </si>
   <si>
+    <t>Manufacturer Part Number</t>
+  </si>
+  <si>
     <t>1uF</t>
   </si>
   <si>
@@ -70,12 +71,12 @@
     <t>Cap0805</t>
   </si>
   <si>
+    <t>Murata</t>
+  </si>
+  <si>
     <t>GCM21BC72A105KE36L</t>
   </si>
   <si>
-    <t>Murata</t>
-  </si>
-  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -88,12 +89,12 @@
     <t>Cap0603</t>
   </si>
   <si>
+    <t>Yageo</t>
+  </si>
+  <si>
     <t>CC0603KRX7R0BB104</t>
   </si>
   <si>
-    <t>Yageo</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -115,12 +116,12 @@
     <t>C18, C19, C29</t>
   </si>
   <si>
+    <t>TDK</t>
+  </si>
+  <si>
     <t>C1608X5R1E475M080AC</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>10pF</t>
   </si>
   <si>
@@ -130,12 +131,12 @@
     <t>C27, C28, C32, C33</t>
   </si>
   <si>
-    <t>06035A100JAT2A</t>
-  </si>
-  <si>
     <t>Kyocera AVX</t>
   </si>
   <si>
+    <t>06035A100JAT2A/4K</t>
+  </si>
+  <si>
     <t>PH254P1x12SMRA-100</t>
   </si>
   <si>
@@ -160,9 +161,6 @@
     <t>HDR1X6 SMD</t>
   </si>
   <si>
-    <t>PH254P1x12SMRA-100_1</t>
-  </si>
-  <si>
     <t>95278-101A26LF</t>
   </si>
   <si>
@@ -274,7 +272,7 @@
     <t>RES SMD 1K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R8, R10, R17, R40</t>
+    <t>R8, R17, R40</t>
   </si>
   <si>
     <t>RC0603FR-071KL</t>
@@ -349,6 +347,9 @@
     <t>Microchip</t>
   </si>
   <si>
+    <t>LAN9255-I/ZMX019</t>
+  </si>
+  <si>
     <t>CAT24C256WI-GT3</t>
   </si>
   <si>
@@ -385,6 +386,9 @@
     <t>Infineon</t>
   </si>
   <si>
+    <t>TLE5012BE5000</t>
+  </si>
+  <si>
     <t>C3E-25.000-8-1015-X-M</t>
   </si>
   <si>
@@ -407,13 +411,19 @@
   </si>
   <si>
     <t>Micro Crystal</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>MFP No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,8 +431,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF24292F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,8 +465,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -459,21 +507,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -788,660 +1000,1443 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D6868A-9F0A-4516-8463-638A210F92F4}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40419B00-65F6-4456-BD8A-5DEE96E1E9D2}">
+  <dimension ref="A1:T28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:20" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="K1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6">
+        <v>4</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="11">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="Q2" s="8" t="str">
+        <f>IF(K2=C2,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="R2" s="8" t="str">
+        <f>IF(L2=G2,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="S2" s="23" t="str">
+        <f>IF(M2=A2,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="T2" s="23" t="str">
+        <f>IF(N2=E2,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="132" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="12">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="8" t="str">
+        <f t="shared" ref="Q3:Q28" si="0">IF(K3=C3,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="R3" s="8" t="str">
+        <f t="shared" ref="R3:R28" si="1">IF(L3=G3,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="S3" s="23" t="str">
+        <f t="shared" ref="S3:S28" si="2">IF(M3=A3,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+      <c r="T3" s="23" t="str">
+        <f t="shared" ref="T3:T28" si="3">IF(N3=E3,"Match","Mismatch")</f>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S4" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T4" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S5" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T5" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6">
+        <v>4</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S6" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T6" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N7" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S7" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T7" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N8" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R8" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S8" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T8" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N9" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S9" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T9" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="6">
+        <v>5</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N10" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R10" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S10" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R11" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S11" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T11" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R12" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S12" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="K13" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R13" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="S13" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T13" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4">
-        <v>24</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="G14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="11">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="Q14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R14" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S14" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T14" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="F15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R15" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S15" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T15" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R16" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S16" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T16" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="6">
+        <v>3</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N17" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R17" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S17" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T17" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R18" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S18" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T18" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="N19" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R19" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S19" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T19" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R20" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S20" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T20" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="36" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="6">
         <v>5</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="4">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="4">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="4">
-        <v>4</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="4">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="K21" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="N21" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R21" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="S21" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Match</v>
+      </c>
+      <c r="T21" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="4">
-        <v>5</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N22" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R22" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S22" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T22" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="7" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="K23" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N23" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R23" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S23" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T23" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="6">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="K24" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N24" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R24" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S24" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T24" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="6">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="K25" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N25" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R25" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S25" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T25" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="E26" s="6">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="G26" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="K26" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N26" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R26" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S26" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T26" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="D27" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G27" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="N27" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R27" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S27" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T27" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="C28" s="7" t="s">
         <v>123</v>
       </c>
+      <c r="D28" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="N28" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Match</v>
+      </c>
+      <c r="R28" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Match</v>
+      </c>
+      <c r="S28" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Mismatch</v>
+      </c>
+      <c r="T28" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v>Match</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="60" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>